--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC473DC-8547-46B8-8CA5-CDF98634A556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC96663B-F29E-4A56-9623-DFE3C9145510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="375" yWindow="3045" windowWidth="17280" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Run Scenarios</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>Run optimal scenarios</t>
+  </si>
+  <si>
+    <t>Figure out why CO2 taxes not applied in 2025</t>
   </si>
 </sst>
 </file>
@@ -458,10 +461,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
@@ -474,7 +479,7 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1"/>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC96663B-F29E-4A56-9623-DFE3C9145510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6284267F-0E25-43E5-930C-FC522BF54423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="3045" windowWidth="17280" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7980" yWindow="5460" windowWidth="17280" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Run Scenarios</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Figure out why CO2 taxes not applied in 2025</t>
+  </si>
+  <si>
+    <t>but…... No C tax in 25/30…. Probably need to find data for and implement a flat tax….</t>
   </si>
 </sst>
 </file>
@@ -136,7 +139,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +485,9 @@
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6284267F-0E25-43E5-930C-FC522BF54423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E3F617-F9A0-41BA-A31B-135ACCDD3194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7980" yWindow="5460" windowWidth="17280" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Run Scenarios</t>
   </si>
@@ -45,18 +45,12 @@
     <t>4100 Mt</t>
   </si>
   <si>
-    <t>Verify 2025 CDR makeup</t>
-  </si>
-  <si>
     <t>Calculate Cost Reductions</t>
   </si>
   <si>
     <t>Update Cost Reduction Code</t>
   </si>
   <si>
-    <t>Validate 2025 C tax</t>
-  </si>
-  <si>
     <t>Run Innovation Scenarios</t>
   </si>
   <si>
@@ -103,12 +97,6 @@
   </si>
   <si>
     <t>Run optimal scenarios</t>
-  </si>
-  <si>
-    <t>Figure out why CO2 taxes not applied in 2025</t>
-  </si>
-  <si>
-    <t>but…... No C tax in 25/30…. Probably need to find data for and implement a flat tax….</t>
   </si>
 </sst>
 </file>
@@ -440,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
@@ -449,147 +437,127 @@
     <col min="4" max="4" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E3F617-F9A0-41BA-A31B-135ACCDD3194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA36488D-20AB-4704-A9F9-FF4D7A019DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7980" yWindow="5460" windowWidth="17280" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -131,6 +131,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -144,10 +150,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,25 +453,25 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1"/>
@@ -476,12 +483,12 @@
       <c r="B6" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -491,7 +498,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -501,7 +508,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -511,7 +518,7 @@
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA36488D-20AB-4704-A9F9-FF4D7A019DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0BEA44-6BDD-487E-8A11-22C82B38A5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
   <si>
     <t>Run Scenarios</t>
   </si>
@@ -78,9 +89,6 @@
     <t>Calculate subsidy cost reductions</t>
   </si>
   <si>
-    <t>Rerun subsidy scenarios another time</t>
-  </si>
-  <si>
     <t>Duplicate subsidy scenarios in utilities.py for cost decrease reasons</t>
   </si>
   <si>
@@ -97,6 +105,93 @@
   </si>
   <si>
     <t>Run optimal scenarios</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Rhodium-6B-l</t>
+  </si>
+  <si>
+    <t>Rhodium-6B-h</t>
+  </si>
+  <si>
+    <t>Rhodium-18B-l</t>
+  </si>
+  <si>
+    <t>Rhodium-18B-h</t>
+  </si>
+  <si>
+    <t>Rhodium-maintain-l</t>
+  </si>
+  <si>
+    <t>Rhodium-maintain-h</t>
+  </si>
+  <si>
+    <t>Rhodium-triple-l</t>
+  </si>
+  <si>
+    <t>Rhodium-triple-h</t>
+  </si>
+  <si>
+    <t>Rhodium-DACS Hubs-l</t>
+  </si>
+  <si>
+    <t>Rhodium-DAC Hubs-h</t>
+  </si>
+  <si>
+    <t>45Q-2040-noCR</t>
+  </si>
+  <si>
+    <t>45Q-2050-noCR</t>
+  </si>
+  <si>
+    <t>CDRIA-2035-noCR</t>
+  </si>
+  <si>
+    <t>CDRIA-2050-noCR</t>
+  </si>
+  <si>
+    <t>45Q-2040-l</t>
+  </si>
+  <si>
+    <t>45Q-2050-l</t>
+  </si>
+  <si>
+    <t>CDRIA-2035-l</t>
+  </si>
+  <si>
+    <t>CDRIA-2050-l</t>
+  </si>
+  <si>
+    <t>45Q-2040-h</t>
+  </si>
+  <si>
+    <t>45Q-2050-h</t>
+  </si>
+  <si>
+    <t>CDRIA-2035-h</t>
+  </si>
+  <si>
+    <t>CDRIA-2050-h</t>
+  </si>
+  <si>
+    <t>Scaling-l</t>
+  </si>
+  <si>
+    <t>Scaling-h</t>
+  </si>
+  <si>
+    <t>3B-l</t>
+  </si>
+  <si>
+    <t>3B-h</t>
+  </si>
+  <si>
+    <t>Rhodium-l</t>
+  </si>
+  <si>
+    <t>Rhodium-h</t>
   </si>
 </sst>
 </file>
@@ -112,7 +207,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -128,12 +223,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -154,7 +243,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
@@ -456,13 +545,17 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -474,7 +567,9 @@
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -483,7 +578,7 @@
       <c r="B6" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -493,78 +588,243 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
+      <c r="A14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>13</v>
+      <c r="A16" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>14</v>
+      <c r="A19" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A0BEA44-6BDD-487E-8A11-22C82B38A5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2463DDDC-DB3B-49DE-9A59-B544F244583D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -207,7 +207,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -223,6 +223,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -243,7 +249,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,10 +564,10 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
+      <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -572,10 +578,10 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="2"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
@@ -588,7 +594,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -598,22 +604,22 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -698,22 +704,22 @@
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="A35" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="A36" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="A37" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="A38" t="s">
         <v>37</v>
       </c>
     </row>
@@ -728,42 +734,42 @@
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="A42" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="A43" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="A44" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="A45" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="A47" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="A48" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="A49" t="s">
         <v>45</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2463DDDC-DB3B-49DE-9A59-B544F244583D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098C06BE-9679-42C0-BF2B-9A47CCCC74C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,7 +207,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,12 +226,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -245,11 +239,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -594,32 +587,32 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098C06BE-9679-42C0-BF2B-9A47CCCC74C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BE5FCB-60D3-42F5-AE22-EB69510BA8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -622,12 +622,12 @@
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -828,5 +828,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BE5FCB-60D3-42F5-AE22-EB69510BA8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB762563-4D1B-47D1-8188-958F43BF556D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="1635" windowWidth="28740" windowHeight="13845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t>Run Scenarios</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>Rhodium-h</t>
+  </si>
+  <si>
+    <t>Run Subsidies both low and high</t>
   </si>
 </sst>
 </file>
@@ -693,7 +696,7 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB762563-4D1B-47D1-8188-958F43BF556D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236C0A1D-C75C-42ED-9BB2-31BF00A41B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="1635" windowWidth="28740" windowHeight="13845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -635,7 +635,7 @@
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -650,22 +650,22 @@
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="A26" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="2" t="s">
         <v>31</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236C0A1D-C75C-42ED-9BB2-31BF00A41B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB4DFB8-35C1-4066-AD5E-62F7783BB1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="1635" windowWidth="28740" windowHeight="13845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -210,7 +210,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -229,6 +229,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -242,10 +248,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -670,12 +677,12 @@
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -695,7 +702,7 @@
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="3" t="s">
         <v>52</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB4DFB8-35C1-4066-AD5E-62F7783BB1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF04D8D-7D38-492D-B84E-B5C8DE67B0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="1635" windowWidth="28740" windowHeight="13845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
   <si>
     <t>Run Scenarios</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>Run Subsidies both low and high</t>
+  </si>
+  <si>
+    <t>has errors</t>
   </si>
 </sst>
 </file>
@@ -231,7 +234,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -647,12 +650,12 @@
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -696,77 +699,80 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -777,12 +783,12 @@
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>15</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF04D8D-7D38-492D-B84E-B5C8DE67B0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FA4BE5-EDA0-4044-8F9C-24359DF2046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="1635" windowWidth="28740" windowHeight="13845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>Run Scenarios</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>has errors</t>
+  </si>
+  <si>
+    <t>Need to update SI</t>
   </si>
 </sst>
 </file>
@@ -213,7 +216,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -238,6 +241,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -251,11 +260,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -733,12 +743,15 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="B40" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -758,7 +771,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="A45" s="3" t="s">
         <v>41</v>
       </c>
     </row>
@@ -778,7 +791,7 @@
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="3" t="s">
         <v>45</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FA4BE5-EDA0-4044-8F9C-24359DF2046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC2AA69-A2BA-45D7-87FF-D3A8BFC97858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="1635" windowWidth="28740" windowHeight="13845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -756,12 +756,12 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="A42" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="2" t="s">
         <v>43</v>
       </c>
     </row>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC2AA69-A2BA-45D7-87FF-D3A8BFC97858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD586ED-C372-4C8A-8CCB-051BD3DFF3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="1635" windowWidth="28740" windowHeight="13845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -216,7 +216,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -247,6 +247,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -260,12 +266,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -751,7 +758,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -766,7 +773,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="A44" s="2" t="s">
         <v>40</v>
       </c>
     </row>
@@ -786,7 +793,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="2" t="s">
         <v>44</v>
       </c>
     </row>
@@ -806,12 +813,12 @@
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="A53" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="A54" s="2" t="s">
         <v>46</v>
       </c>
     </row>
